--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/15.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/15.xlsx
@@ -426,13 +426,13 @@
         <v>-10.74556073740594</v>
       </c>
       <c r="E2">
-        <v>-15.0126405766659</v>
+        <v>-15.02206005995061</v>
       </c>
       <c r="F2">
-        <v>1.808353229188105</v>
+        <v>-0.7544183636316987</v>
       </c>
       <c r="G2">
-        <v>-17.32943150969656</v>
+        <v>-17.32904642486937</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.26026136238635</v>
       </c>
       <c r="E3">
-        <v>-15.09043022477994</v>
+        <v>-14.76538329365356</v>
       </c>
       <c r="F3">
-        <v>1.698886133642956</v>
+        <v>-0.6382390070216653</v>
       </c>
       <c r="G3">
-        <v>-16.6727626710445</v>
+        <v>-16.6865108520613</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.658842357335418</v>
       </c>
       <c r="E4">
-        <v>-14.90321176467932</v>
+        <v>-15.59302694004274</v>
       </c>
       <c r="F4">
-        <v>2.161767897918486</v>
+        <v>-0.4012025030779895</v>
       </c>
       <c r="G4">
-        <v>-17.24549346034767</v>
+        <v>-16.56709800520836</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.015532565663545</v>
       </c>
       <c r="E5">
-        <v>-14.66097156094737</v>
+        <v>-15.72325088113274</v>
       </c>
       <c r="F5">
-        <v>2.494730175473748</v>
+        <v>-0.4612674234549817</v>
       </c>
       <c r="G5">
-        <v>-16.52250779296445</v>
+        <v>-16.03819770147309</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.356535477055179</v>
       </c>
       <c r="E6">
-        <v>-15.48049983240784</v>
+        <v>-14.97387865537127</v>
       </c>
       <c r="F6">
-        <v>1.831832474853055</v>
+        <v>0.127436722366571</v>
       </c>
       <c r="G6">
-        <v>-15.56700529617978</v>
+        <v>-15.96712148535233</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.720047975717298</v>
       </c>
       <c r="E7">
-        <v>-16.0985599757122</v>
+        <v>-17.90174312376771</v>
       </c>
       <c r="F7">
-        <v>1.590139717738243</v>
+        <v>-0.4464736100083853</v>
       </c>
       <c r="G7">
-        <v>-15.73856254475102</v>
+        <v>-15.37111329727478</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.134563412452595</v>
       </c>
       <c r="E8">
-        <v>-17.26705352231873</v>
+        <v>-17.2067281278256</v>
       </c>
       <c r="F8">
-        <v>1.789232852796687</v>
+        <v>-0.1958154324930745</v>
       </c>
       <c r="G8">
-        <v>-14.1275033865101</v>
+        <v>-15.37183516815422</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.616402911146367</v>
       </c>
       <c r="E9">
-        <v>-16.85386714045684</v>
+        <v>-19.18479469834698</v>
       </c>
       <c r="F9">
-        <v>2.141502717776399</v>
+        <v>0.04888926849831627</v>
       </c>
       <c r="G9">
-        <v>-13.48902099467973</v>
+        <v>-14.72545266319114</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.178160066465157</v>
       </c>
       <c r="E10">
-        <v>-17.81773196508907</v>
+        <v>-18.66515320380709</v>
       </c>
       <c r="F10">
-        <v>2.842705783837347</v>
+        <v>0.4764386779422391</v>
       </c>
       <c r="G10">
-        <v>-14.13422474845992</v>
+        <v>-14.64366978350222</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.815744244975292</v>
       </c>
       <c r="E11">
-        <v>-17.11703122284327</v>
+        <v>-19.62813754763846</v>
       </c>
       <c r="F11">
-        <v>2.588736621813047</v>
+        <v>0.9635725546695304</v>
       </c>
       <c r="G11">
-        <v>-13.27344006544085</v>
+        <v>-14.37529046102496</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.530628131118356</v>
       </c>
       <c r="E12">
-        <v>-19.20993408649617</v>
+        <v>-20.05645823156803</v>
       </c>
       <c r="F12">
-        <v>3.026523823988169</v>
+        <v>0.8624769400970731</v>
       </c>
       <c r="G12">
-        <v>-12.66754237685216</v>
+        <v>-13.20490149306265</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.307062928844537</v>
       </c>
       <c r="E13">
-        <v>-18.85711463124066</v>
+        <v>-20.22399877641161</v>
       </c>
       <c r="F13">
-        <v>2.779290945683434</v>
+        <v>1.276445265972098</v>
       </c>
       <c r="G13">
-        <v>-12.48046816780365</v>
+        <v>-13.18477787375435</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.1404092217598</v>
       </c>
       <c r="E14">
-        <v>-20.49336360330601</v>
+        <v>-20.23354285603606</v>
       </c>
       <c r="F14">
-        <v>3.456373609709666</v>
+        <v>1.61120675752624</v>
       </c>
       <c r="G14">
-        <v>-11.34326698508357</v>
+        <v>-13.40271630535901</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.009204444355958</v>
       </c>
       <c r="E15">
-        <v>-21.16903294089707</v>
+        <v>-21.38353799940181</v>
       </c>
       <c r="F15">
-        <v>3.827521967799179</v>
+        <v>1.576292728233046</v>
       </c>
       <c r="G15">
-        <v>-11.8400120530624</v>
+        <v>-13.17975741190564</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.903069197007662</v>
       </c>
       <c r="E16">
-        <v>-21.29019457487629</v>
+        <v>-21.77056745633994</v>
       </c>
       <c r="F16">
-        <v>4.216690630369192</v>
+        <v>1.873520892766342</v>
       </c>
       <c r="G16">
-        <v>-10.88490900020017</v>
+        <v>-13.04012173744994</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.798755343889654</v>
       </c>
       <c r="E17">
-        <v>-22.18896196520316</v>
+        <v>-22.2697626915277</v>
       </c>
       <c r="F17">
-        <v>3.51980335847683</v>
+        <v>1.93525911529699</v>
       </c>
       <c r="G17">
-        <v>-10.97275402882966</v>
+        <v>-12.41056809212118</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.683833067074049</v>
       </c>
       <c r="E18">
-        <v>-23.62368051094253</v>
+        <v>-23.86730373404565</v>
       </c>
       <c r="F18">
-        <v>4.177265312200352</v>
+        <v>2.268748234520432</v>
       </c>
       <c r="G18">
-        <v>-11.20445891666325</v>
+        <v>-12.64192444555187</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.540098050070881</v>
       </c>
       <c r="E19">
-        <v>-24.12047518998455</v>
+        <v>-24.37479708546043</v>
       </c>
       <c r="F19">
-        <v>4.114579437360902</v>
+        <v>2.68307275837866</v>
       </c>
       <c r="G19">
-        <v>-10.96414901465735</v>
+        <v>-11.99959773231108</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.362077117601515</v>
       </c>
       <c r="E20">
-        <v>-24.01276165427512</v>
+        <v>-24.99079308273634</v>
       </c>
       <c r="F20">
-        <v>4.761474736494315</v>
+        <v>2.301410761212816</v>
       </c>
       <c r="G20">
-        <v>-10.19524426603332</v>
+        <v>-12.23292389253576</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.142211804045893</v>
       </c>
       <c r="E21">
-        <v>-24.28347212163877</v>
+        <v>-26.45221262408304</v>
       </c>
       <c r="F21">
-        <v>4.968390973304798</v>
+        <v>2.770279965075781</v>
       </c>
       <c r="G21">
-        <v>-9.91430465132821</v>
+        <v>-11.77353727428347</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.883634410438724</v>
       </c>
       <c r="E22">
-        <v>-25.80832781276089</v>
+        <v>-26.15660365482704</v>
       </c>
       <c r="F22">
-        <v>5.134594609002491</v>
+        <v>2.802612801541851</v>
       </c>
       <c r="G22">
-        <v>-10.53538643045881</v>
+        <v>-11.38290722558273</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.587325358527054</v>
       </c>
       <c r="E23">
-        <v>-25.05150887909401</v>
+        <v>-27.52698480393349</v>
       </c>
       <c r="F23">
-        <v>4.952299108138015</v>
+        <v>2.502820011529488</v>
       </c>
       <c r="G23">
-        <v>-9.750588774136384</v>
+        <v>-11.14076458087386</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.262998304905709</v>
       </c>
       <c r="E24">
-        <v>-25.21953950287392</v>
+        <v>-27.54433692084863</v>
       </c>
       <c r="F24">
-        <v>5.157165963993972</v>
+        <v>2.881022746421241</v>
       </c>
       <c r="G24">
-        <v>-9.149714158141</v>
+        <v>-10.870770512867</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.917029877283038</v>
       </c>
       <c r="E25">
-        <v>-27.75653694706809</v>
+        <v>-29.02496714117831</v>
       </c>
       <c r="F25">
-        <v>5.487865141804785</v>
+        <v>2.945052233188032</v>
       </c>
       <c r="G25">
-        <v>-9.132881382389797</v>
+        <v>-11.28661252208411</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.5608617356829</v>
       </c>
       <c r="E26">
-        <v>-26.45155226348239</v>
+        <v>-28.51654554703244</v>
       </c>
       <c r="F26">
-        <v>5.676108320621361</v>
+        <v>2.892682845983047</v>
       </c>
       <c r="G26">
-        <v>-9.838337205215996</v>
+        <v>-11.07850354386499</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.199642503311662</v>
       </c>
       <c r="E27">
-        <v>-27.10016342929219</v>
+        <v>-29.30603987079741</v>
       </c>
       <c r="F27">
-        <v>4.647648771675635</v>
+        <v>2.886748421909391</v>
       </c>
       <c r="G27">
-        <v>-9.020009756109902</v>
+        <v>-10.72382475355619</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.841027605714988</v>
       </c>
       <c r="E28">
-        <v>-26.76834261049501</v>
+        <v>-30.52175750677291</v>
       </c>
       <c r="F28">
-        <v>4.937380211213595</v>
+        <v>2.731368234696677</v>
       </c>
       <c r="G28">
-        <v>-8.490121285546889</v>
+        <v>-10.12590027894876</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.487949807868201</v>
       </c>
       <c r="E29">
-        <v>-26.0254867733022</v>
+        <v>-29.58627365172889</v>
       </c>
       <c r="F29">
-        <v>4.623120812878741</v>
+        <v>3.237159430437222</v>
       </c>
       <c r="G29">
-        <v>-8.903291197674999</v>
+        <v>-9.620702925356202</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.146695715016918</v>
       </c>
       <c r="E30">
-        <v>-26.96222697477198</v>
+        <v>-30.2305966268458</v>
       </c>
       <c r="F30">
-        <v>4.346177709305199</v>
+        <v>2.823300449059366</v>
       </c>
       <c r="G30">
-        <v>-8.84214103248965</v>
+        <v>-9.523793391506372</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.8217054888030746</v>
       </c>
       <c r="E31">
-        <v>-27.6322687110179</v>
+        <v>-30.93008878459608</v>
       </c>
       <c r="F31">
-        <v>4.514149081040467</v>
+        <v>3.307469598852038</v>
       </c>
       <c r="G31">
-        <v>-8.397027354916972</v>
+        <v>-8.932799138416058</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.5205459674643726</v>
       </c>
       <c r="E32">
-        <v>-27.43096255810346</v>
+        <v>-29.93901211936356</v>
       </c>
       <c r="F32">
-        <v>5.433439746706052</v>
+        <v>2.971301539447943</v>
       </c>
       <c r="G32">
-        <v>-8.52787787382357</v>
+        <v>-9.001748903067361</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.2502918992140193</v>
       </c>
       <c r="E33">
-        <v>-28.96615351560742</v>
+        <v>-30.81159143568173</v>
       </c>
       <c r="F33">
-        <v>5.312011025864478</v>
+        <v>2.793982869939486</v>
       </c>
       <c r="G33">
-        <v>-7.792425901017775</v>
+        <v>-8.551093920100044</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.01784033409655829</v>
       </c>
       <c r="E34">
-        <v>-27.15001857803543</v>
+        <v>-30.72680777969668</v>
       </c>
       <c r="F34">
-        <v>4.871829841895265</v>
+        <v>2.694635110586936</v>
       </c>
       <c r="G34">
-        <v>-8.468411638899488</v>
+        <v>-8.289374607074711</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.1715655300090328</v>
       </c>
       <c r="E35">
-        <v>-26.98317992590574</v>
+        <v>-29.96010420307671</v>
       </c>
       <c r="F35">
-        <v>4.626023412258151</v>
+        <v>2.859872869892964</v>
       </c>
       <c r="G35">
-        <v>-7.692643242745425</v>
+        <v>-8.399935724391472</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.3147798089922967</v>
       </c>
       <c r="E36">
-        <v>-28.9683754836662</v>
+        <v>-29.75350685893444</v>
       </c>
       <c r="F36">
-        <v>4.497608240741366</v>
+        <v>3.022168268184249</v>
       </c>
       <c r="G36">
-        <v>-7.909918545223942</v>
+        <v>-7.666752488635355</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.41003468559811</v>
       </c>
       <c r="E37">
-        <v>-25.60482045784429</v>
+        <v>-29.97117458786304</v>
       </c>
       <c r="F37">
-        <v>5.057516678906802</v>
+        <v>3.10943180386476</v>
       </c>
       <c r="G37">
-        <v>-8.561056521459733</v>
+        <v>-7.515686974359767</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.4592444268864626</v>
       </c>
       <c r="E38">
-        <v>-26.99035252186372</v>
+        <v>-30.03229324571921</v>
       </c>
       <c r="F38">
-        <v>4.724203173572754</v>
+        <v>2.998856352734665</v>
       </c>
       <c r="G38">
-        <v>-8.045311759719077</v>
+        <v>-7.475865287111516</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.4646384197493226</v>
       </c>
       <c r="E39">
-        <v>-25.8837044450952</v>
+        <v>-29.5373550521394</v>
       </c>
       <c r="F39">
-        <v>4.934810615530111</v>
+        <v>3.368230347847382</v>
       </c>
       <c r="G39">
-        <v>-8.178821321991723</v>
+        <v>-7.079021666283932</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.4317492445442668</v>
       </c>
       <c r="E40">
-        <v>-26.26031764803066</v>
+        <v>-29.26321403222144</v>
       </c>
       <c r="F40">
-        <v>4.896861448073061</v>
+        <v>3.275216285656636</v>
       </c>
       <c r="G40">
-        <v>-7.706074218294408</v>
+        <v>-7.534544382541378</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.3654596469963878</v>
       </c>
       <c r="E41">
-        <v>-25.76979847130046</v>
+        <v>-29.36684080798724</v>
       </c>
       <c r="F41">
-        <v>4.777831679229994</v>
+        <v>3.519516743355461</v>
       </c>
       <c r="G41">
-        <v>-8.331782236840459</v>
+        <v>-7.212120036283478</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.270863728416503</v>
       </c>
       <c r="E42">
-        <v>-25.68308357204936</v>
+        <v>-29.28807930842319</v>
       </c>
       <c r="F42">
-        <v>4.993145904770058</v>
+        <v>3.52049587362557</v>
       </c>
       <c r="G42">
-        <v>-7.501863081749821</v>
+        <v>-7.599922648592036</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.1515835448235936</v>
       </c>
       <c r="E43">
-        <v>-25.35406201768512</v>
+        <v>-28.10183078340301</v>
       </c>
       <c r="F43">
-        <v>4.883995245572779</v>
+        <v>3.625231334565928</v>
       </c>
       <c r="G43">
-        <v>-7.824352696622499</v>
+        <v>-7.582300122602022</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.01043681697675852</v>
       </c>
       <c r="E44">
-        <v>-25.1904462575435</v>
+        <v>-28.72494123167836</v>
       </c>
       <c r="F44">
-        <v>5.097092759942951</v>
+        <v>3.781310663866606</v>
       </c>
       <c r="G44">
-        <v>-7.861694176509193</v>
+        <v>-7.682662366173599</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.1494033011327663</v>
       </c>
       <c r="E45">
-        <v>-24.76771164284583</v>
+        <v>-28.78771702085314</v>
       </c>
       <c r="F45">
-        <v>5.043623300827049</v>
+        <v>3.72726631777316</v>
       </c>
       <c r="G45">
-        <v>-7.636166310378167</v>
+        <v>-7.172008556385614</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.32534555885977</v>
       </c>
       <c r="E46">
-        <v>-24.14051858783817</v>
+        <v>-27.40953614087866</v>
       </c>
       <c r="F46">
-        <v>4.903614299140682</v>
+        <v>3.679320412499125</v>
       </c>
       <c r="G46">
-        <v>-7.759329491836231</v>
+        <v>-8.016701915117361</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.5126100144796515</v>
       </c>
       <c r="E47">
-        <v>-23.61763758846491</v>
+        <v>-26.90090065634956</v>
       </c>
       <c r="F47">
-        <v>5.141884242147126</v>
+        <v>3.720296434446005</v>
       </c>
       <c r="G47">
-        <v>-7.388201705231114</v>
+        <v>-7.842279374357378</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.7089220353549136</v>
       </c>
       <c r="E48">
-        <v>-24.02718160399493</v>
+        <v>-27.04206415606916</v>
       </c>
       <c r="F48">
-        <v>4.784677307446729</v>
+        <v>3.459097281730071</v>
       </c>
       <c r="G48">
-        <v>-7.923549242734144</v>
+        <v>-8.542503265022987</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.909242553370436</v>
       </c>
       <c r="E49">
-        <v>-22.93799778084731</v>
+        <v>-26.72156083813214</v>
       </c>
       <c r="F49">
-        <v>4.946611537550393</v>
+        <v>3.77861349960309</v>
       </c>
       <c r="G49">
-        <v>-7.969781613325874</v>
+        <v>-7.771378078124219</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.112267696577776</v>
       </c>
       <c r="E50">
-        <v>-22.43695436662</v>
+        <v>-26.88999017019924</v>
       </c>
       <c r="F50">
-        <v>5.419460218416407</v>
+        <v>3.644744357106273</v>
       </c>
       <c r="G50">
-        <v>-8.316485884281127</v>
+        <v>-8.059461995402911</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.313475015433942</v>
       </c>
       <c r="E51">
-        <v>-21.5952562531076</v>
+        <v>-26.3943459306942</v>
       </c>
       <c r="F51">
-        <v>5.247453040694701</v>
+        <v>3.71459892344955</v>
       </c>
       <c r="G51">
-        <v>-8.023950647474587</v>
+        <v>-8.764537954891102</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.512984336828168</v>
       </c>
       <c r="E52">
-        <v>-20.97463773162714</v>
+        <v>-25.23396775901638</v>
       </c>
       <c r="F52">
-        <v>5.456619123371187</v>
+        <v>3.696071658118536</v>
       </c>
       <c r="G52">
-        <v>-8.866926136265382</v>
+        <v>-8.473855041371959</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.706930004649639</v>
       </c>
       <c r="E53">
-        <v>-24.04855818268382</v>
+        <v>-25.65000739705843</v>
       </c>
       <c r="F53">
-        <v>4.899687837651412</v>
+        <v>3.583484930934445</v>
       </c>
       <c r="G53">
-        <v>-8.402506002441424</v>
+        <v>-8.733158110278216</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.896209257692936</v>
       </c>
       <c r="E54">
-        <v>-20.59377579350639</v>
+        <v>-25.0941623594</v>
       </c>
       <c r="F54">
-        <v>4.705856492335551</v>
+        <v>3.844969042036942</v>
       </c>
       <c r="G54">
-        <v>-9.051328248224896</v>
+        <v>-8.402123528358825</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.077071462051914</v>
       </c>
       <c r="E55">
-        <v>-20.90821126969784</v>
+        <v>-24.56329473464909</v>
       </c>
       <c r="F55">
-        <v>4.456115317535139</v>
+        <v>3.841354046691125</v>
       </c>
       <c r="G55">
-        <v>-9.556893716804803</v>
+        <v>-9.173988861349173</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.250741208695639</v>
       </c>
       <c r="E56">
-        <v>-21.02502864463129</v>
+        <v>-23.50488205420714</v>
       </c>
       <c r="F56">
-        <v>4.608089257987541</v>
+        <v>3.876844619696667</v>
       </c>
       <c r="G56">
-        <v>-9.752264872163879</v>
+        <v>-9.099078766796358</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.413279245412204</v>
       </c>
       <c r="E57">
-        <v>-20.85544056660456</v>
+        <v>-24.05066386082551</v>
       </c>
       <c r="F57">
-        <v>4.262027178324409</v>
+        <v>4.019431500740546</v>
       </c>
       <c r="G57">
-        <v>-9.976217153934167</v>
+        <v>-8.987541231002522</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.566159197881658</v>
       </c>
       <c r="E58">
-        <v>-20.29341139728347</v>
+        <v>-23.88731390620868</v>
       </c>
       <c r="F58">
-        <v>4.631803759994886</v>
+        <v>4.266666035780086</v>
       </c>
       <c r="G58">
-        <v>-9.347244399276928</v>
+        <v>-9.342289206042995</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.705949779610504</v>
       </c>
       <c r="E59">
-        <v>-20.51769726845818</v>
+        <v>-23.39863460209537</v>
       </c>
       <c r="F59">
-        <v>4.712074218060963</v>
+        <v>4.18740784268023</v>
       </c>
       <c r="G59">
-        <v>-9.501271803291134</v>
+        <v>-8.994102032159988</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.835287530307208</v>
       </c>
       <c r="E60">
-        <v>-21.10873661888321</v>
+        <v>-24.11265053984857</v>
       </c>
       <c r="F60">
-        <v>5.030261734619893</v>
+        <v>4.218426888445459</v>
       </c>
       <c r="G60">
-        <v>-10.00093829446742</v>
+        <v>-9.62719323640971</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.951818554904112</v>
       </c>
       <c r="E61">
-        <v>-19.60007845192792</v>
+        <v>-23.3023548571632</v>
       </c>
       <c r="F61">
-        <v>5.086075473485718</v>
+        <v>4.51515637580227</v>
       </c>
       <c r="G61">
-        <v>-9.524040106870233</v>
+        <v>-9.649307548468736</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.059134524854989</v>
       </c>
       <c r="E62">
-        <v>-19.12174064401344</v>
+        <v>-23.2864812834797</v>
       </c>
       <c r="F62">
-        <v>4.65329326715831</v>
+        <v>4.357549537010831</v>
       </c>
       <c r="G62">
-        <v>-9.647325993324079</v>
+        <v>-10.11730179163793</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.156438306413739</v>
       </c>
       <c r="E63">
-        <v>-17.98692964125126</v>
+        <v>-22.74888130317125</v>
       </c>
       <c r="F63">
-        <v>5.115954685704696</v>
+        <v>4.226649263285648</v>
       </c>
       <c r="G63">
-        <v>-10.65213631782881</v>
+        <v>-10.29641714580044</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.248894257970512</v>
       </c>
       <c r="E64">
-        <v>-18.46844050261791</v>
+        <v>-22.72796157772808</v>
       </c>
       <c r="F64">
-        <v>4.595981840028224</v>
+        <v>4.115151010868834</v>
       </c>
       <c r="G64">
-        <v>-11.10491775226558</v>
+        <v>-10.63280897562079</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.337681511277559</v>
       </c>
       <c r="E65">
-        <v>-18.52771098143454</v>
+        <v>-22.38179141380363</v>
       </c>
       <c r="F65">
-        <v>5.120954711347994</v>
+        <v>4.15919696241049</v>
       </c>
       <c r="G65">
-        <v>-10.05340903925961</v>
+        <v>-10.59276015359312</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.428891219189446</v>
       </c>
       <c r="E66">
-        <v>-19.13260544483919</v>
+        <v>-22.60849860718072</v>
       </c>
       <c r="F66">
-        <v>4.620359035957808</v>
+        <v>4.614658211491742</v>
       </c>
       <c r="G66">
-        <v>-10.17387532155506</v>
+        <v>-11.26849395462179</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.524606766391084</v>
       </c>
       <c r="E67">
-        <v>-19.59171388431971</v>
+        <v>-23.32737795539529</v>
       </c>
       <c r="F67">
-        <v>5.100129554841614</v>
+        <v>4.113023763378445</v>
       </c>
       <c r="G67">
-        <v>-10.38995490301085</v>
+        <v>-11.00171501857887</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.62999048123794</v>
       </c>
       <c r="E68">
-        <v>-18.67738441115871</v>
+        <v>-22.47840341564179</v>
       </c>
       <c r="F68">
-        <v>4.167190707847505</v>
+        <v>4.384927079673355</v>
       </c>
       <c r="G68">
-        <v>-11.02759532971058</v>
+        <v>-11.15281708327874</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.745739681148164</v>
       </c>
       <c r="E69">
-        <v>-17.45982482596065</v>
+        <v>-22.85055606961437</v>
       </c>
       <c r="F69">
-        <v>4.669963332772248</v>
+        <v>4.696035368407959</v>
       </c>
       <c r="G69">
-        <v>-11.18585344533469</v>
+        <v>-11.20614806841371</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.874558953216872</v>
       </c>
       <c r="E70">
-        <v>-19.61958608552063</v>
+        <v>-22.03406794884368</v>
       </c>
       <c r="F70">
-        <v>5.041509307215104</v>
+        <v>4.779478473626759</v>
       </c>
       <c r="G70">
-        <v>-10.69858799096619</v>
+        <v>-11.57147086442048</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.014819508021505</v>
       </c>
       <c r="E71">
-        <v>-18.82805876481216</v>
+        <v>-22.11902188649305</v>
       </c>
       <c r="F71">
-        <v>4.956843531709772</v>
+        <v>4.654802552566212</v>
       </c>
       <c r="G71">
-        <v>-10.67641232640927</v>
+        <v>-12.3452838128758</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.166321412666928</v>
       </c>
       <c r="E72">
-        <v>-20.69669237013564</v>
+        <v>-21.84235986730092</v>
       </c>
       <c r="F72">
-        <v>5.332572761536767</v>
+        <v>4.266677632923725</v>
       </c>
       <c r="G72">
-        <v>-11.03037707807241</v>
+        <v>-12.17314175751616</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.325425437604961</v>
       </c>
       <c r="E73">
-        <v>-20.45768751802574</v>
+        <v>-22.17564676969576</v>
       </c>
       <c r="F73">
-        <v>4.564293473401531</v>
+        <v>4.788378453002437</v>
       </c>
       <c r="G73">
-        <v>-10.60397982847343</v>
+        <v>-12.13580941523553</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.490297242427403</v>
       </c>
       <c r="E74">
-        <v>-19.21645878148748</v>
+        <v>-21.48133781967888</v>
       </c>
       <c r="F74">
-        <v>4.784925817667569</v>
+        <v>4.603882808316126</v>
       </c>
       <c r="G74">
-        <v>-11.20401247933818</v>
+        <v>-12.40176857747683</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.65709560611406</v>
       </c>
       <c r="E75">
-        <v>-19.17321139196204</v>
+        <v>-21.97810757945294</v>
       </c>
       <c r="F75">
-        <v>4.422896127948073</v>
+        <v>4.794549790153294</v>
       </c>
       <c r="G75">
-        <v>-9.761329377384223</v>
+        <v>-12.54582946401446</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.823682680787568</v>
       </c>
       <c r="E76">
-        <v>-20.80622916561667</v>
+        <v>-22.14220511210824</v>
       </c>
       <c r="F76">
-        <v>4.672168446798501</v>
+        <v>4.831428706925927</v>
       </c>
       <c r="G76">
-        <v>-11.2099088459972</v>
+        <v>-12.9375468878374</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.986071971309805</v>
       </c>
       <c r="E77">
-        <v>-20.67205967376809</v>
+        <v>-22.93991656447939</v>
       </c>
       <c r="F77">
-        <v>4.250647066944749</v>
+        <v>4.865202902672869</v>
       </c>
       <c r="G77">
-        <v>-10.7803734813997</v>
+        <v>-12.34720662626716</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.142031364615736</v>
       </c>
       <c r="E78">
-        <v>-19.77953456006243</v>
+        <v>-23.25902855662259</v>
       </c>
       <c r="F78">
-        <v>4.414074015108258</v>
+        <v>4.439708672755292</v>
       </c>
       <c r="G78">
-        <v>-10.30616305535906</v>
+        <v>-12.47738357306925</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.287872868813552</v>
       </c>
       <c r="E79">
-        <v>-20.01097641434983</v>
+        <v>-22.87903463966872</v>
       </c>
       <c r="F79">
-        <v>4.448497650898995</v>
+        <v>4.647375410432711</v>
       </c>
       <c r="G79">
-        <v>-9.705814504398791</v>
+        <v>-12.56900373837748</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.422031209293491</v>
       </c>
       <c r="E80">
-        <v>-21.03796589790813</v>
+        <v>-23.35684498974495</v>
       </c>
       <c r="F80">
-        <v>4.640229913216163</v>
+        <v>4.284171095736045</v>
       </c>
       <c r="G80">
-        <v>-10.11180747964593</v>
+        <v>-12.13060359052085</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.542162159800185</v>
       </c>
       <c r="E81">
-        <v>-22.16118113465139</v>
+        <v>-23.37938031439347</v>
       </c>
       <c r="F81">
-        <v>5.148784542612447</v>
+        <v>4.64901723462506</v>
       </c>
       <c r="G81">
-        <v>-10.91361022086257</v>
+        <v>-12.42907957664447</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.648129632804777</v>
       </c>
       <c r="E82">
-        <v>-23.02053454950563</v>
+        <v>-24.83103980912681</v>
       </c>
       <c r="F82">
-        <v>4.276917910757133</v>
+        <v>4.597728038513325</v>
       </c>
       <c r="G82">
-        <v>-10.69867545090999</v>
+        <v>-12.14867124846365</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.738504411125384</v>
       </c>
       <c r="E83">
-        <v>-22.81929900118372</v>
+        <v>-25.5314539797912</v>
       </c>
       <c r="F83">
-        <v>4.489016414039529</v>
+        <v>5.081632110737101</v>
       </c>
       <c r="G83">
-        <v>-9.73327170526353</v>
+        <v>-12.25390644681454</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.812261690950492</v>
       </c>
       <c r="E84">
-        <v>-24.80078781783676</v>
+        <v>-26.39035469461104</v>
       </c>
       <c r="F84">
-        <v>5.01299524447594</v>
+        <v>4.457280002103475</v>
       </c>
       <c r="G84">
-        <v>-9.941308888006391</v>
+        <v>-12.0173377418077</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.867730610096276</v>
       </c>
       <c r="E85">
-        <v>-23.84275410190459</v>
+        <v>-27.65404399799397</v>
       </c>
       <c r="F85">
-        <v>4.676956410386682</v>
+        <v>4.807956088200201</v>
       </c>
       <c r="G85">
-        <v>-10.78128593663429</v>
+        <v>-12.34967769602264</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.903691572957054</v>
       </c>
       <c r="E86">
-        <v>-26.39035884782237</v>
+        <v>-27.84056887180335</v>
       </c>
       <c r="F86">
-        <v>4.65389963209716</v>
+        <v>5.371148174750334</v>
       </c>
       <c r="G86">
-        <v>-9.57676278851547</v>
+        <v>-12.06788306246395</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.919595429701011</v>
       </c>
       <c r="E87">
-        <v>-27.18387970996676</v>
+        <v>-29.05949486352727</v>
       </c>
       <c r="F87">
-        <v>4.910348926125442</v>
+        <v>4.785807200584148</v>
       </c>
       <c r="G87">
-        <v>-10.50587848971775</v>
+        <v>-11.88355274598069</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.915114360364514</v>
       </c>
       <c r="E88">
-        <v>-28.77739629071095</v>
+        <v>-29.89225318966298</v>
       </c>
       <c r="F88">
-        <v>5.245658796900237</v>
+        <v>5.452613138611249</v>
       </c>
       <c r="G88">
-        <v>-9.758242171905232</v>
+        <v>-12.00796255798101</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.890825184286751</v>
       </c>
       <c r="E89">
-        <v>-28.69663086668267</v>
+        <v>-31.65899813816011</v>
       </c>
       <c r="F89">
-        <v>4.530819146654403</v>
+        <v>5.409190119356499</v>
       </c>
       <c r="G89">
-        <v>-9.862109340090379</v>
+        <v>-11.87860930109741</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.846388318233946</v>
       </c>
       <c r="E90">
-        <v>-32.45175480942073</v>
+        <v>-32.42000143223675</v>
       </c>
       <c r="F90">
-        <v>5.207383252686483</v>
+        <v>5.548306140982648</v>
       </c>
       <c r="G90">
-        <v>-8.977988516543638</v>
+        <v>-11.50682621759993</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.7819594678192</v>
       </c>
       <c r="E91">
-        <v>-32.03958596433342</v>
+        <v>-34.09746272027838</v>
       </c>
       <c r="F91">
-        <v>4.838937029064902</v>
+        <v>5.370578257977209</v>
       </c>
       <c r="G91">
-        <v>-9.196513060309002</v>
+        <v>-10.75192419759034</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.695814693327051</v>
       </c>
       <c r="E92">
-        <v>-34.09030881377136</v>
+        <v>-35.63508745961869</v>
       </c>
       <c r="F92">
-        <v>4.548955422571296</v>
+        <v>5.262487909055512</v>
       </c>
       <c r="G92">
-        <v>-9.417844154509813</v>
+        <v>-11.22919572166405</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.58801577719315</v>
       </c>
       <c r="E93">
-        <v>-36.37236138079093</v>
+        <v>-37.63221519351538</v>
       </c>
       <c r="F93">
-        <v>5.403259008752454</v>
+        <v>5.910746700933932</v>
       </c>
       <c r="G93">
-        <v>-9.239438922876086</v>
+        <v>-11.29836348348871</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.457594260225304</v>
       </c>
       <c r="E94">
-        <v>-37.55567981522144</v>
+        <v>-39.96923758902471</v>
       </c>
       <c r="F94">
-        <v>4.61527617357423</v>
+        <v>5.698479210701365</v>
       </c>
       <c r="G94">
-        <v>-9.424924493840912</v>
+        <v>-11.26102461434661</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.30705344697764</v>
       </c>
       <c r="E95">
-        <v>-39.21971169444423</v>
+        <v>-42.24028414603348</v>
       </c>
       <c r="F95">
-        <v>5.097667646920494</v>
+        <v>5.475976412839806</v>
       </c>
       <c r="G95">
-        <v>-8.198600323013997</v>
+        <v>-11.15448143295557</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.137778232248515</v>
       </c>
       <c r="E96">
-        <v>-43.02340952023182</v>
+        <v>-43.6895140121418</v>
       </c>
       <c r="F96">
-        <v>4.961901543071266</v>
+        <v>5.797947911694724</v>
       </c>
       <c r="G96">
-        <v>-8.689015640731673</v>
+        <v>-10.91170698805565</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.954169408350762</v>
       </c>
       <c r="E97">
-        <v>-44.38609892196469</v>
+        <v>-46.9401193410765</v>
       </c>
       <c r="F97">
-        <v>4.525318787099815</v>
+        <v>5.763014001583863</v>
       </c>
       <c r="G97">
-        <v>-7.992945444710526</v>
+        <v>-11.05457606968744</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.761294701277215</v>
       </c>
       <c r="E98">
-        <v>-46.62808442103081</v>
+        <v>-48.45676932492359</v>
       </c>
       <c r="F98">
-        <v>4.609691320544556</v>
+        <v>5.661659936381732</v>
       </c>
       <c r="G98">
-        <v>-9.017878083151258</v>
+        <v>-10.87597764295397</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.568345196483427</v>
       </c>
       <c r="E99">
-        <v>-49.97191169305977</v>
+        <v>-50.60213036251757</v>
       </c>
       <c r="F99">
-        <v>4.793312209253511</v>
+        <v>5.61452583116244</v>
       </c>
       <c r="G99">
-        <v>-8.325503396098831</v>
+        <v>-10.99274188941922</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.387063230089272</v>
       </c>
       <c r="E100">
-        <v>-50.85676478714564</v>
+        <v>-52.98691780317092</v>
       </c>
       <c r="F100">
-        <v>4.229147619372491</v>
+        <v>5.484899586502762</v>
       </c>
       <c r="G100">
-        <v>-8.536895385641275</v>
+        <v>-10.08570917134087</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.231861436945187</v>
       </c>
       <c r="E101">
-        <v>-54.3030907189143</v>
+        <v>-54.67503519316922</v>
       </c>
       <c r="F101">
-        <v>3.403540336759113</v>
+        <v>5.872467843250567</v>
       </c>
       <c r="G101">
-        <v>-8.872916489729693</v>
+        <v>-10.31373943616248</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.121229761605278</v>
       </c>
       <c r="E102">
-        <v>-54.85300808570936</v>
+        <v>-56.8257995586968</v>
       </c>
       <c r="F102">
-        <v>3.774440184627786</v>
+        <v>5.741398582575212</v>
       </c>
       <c r="G102">
-        <v>-8.713439156381538</v>
+        <v>-10.65331898512858</v>
       </c>
     </row>
   </sheetData>
